--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R608b603e66bf4314"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3bbfb5e55da4100"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra3bbfb5e55da4100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e4702ee1a0043fe"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2e4702ee1a0043fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7443b28f8b044498"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7443b28f8b044498"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdbcdf90b54e14bb5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdbcdf90b54e14bb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R41a75dce1b0149d2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R41a75dce1b0149d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra28905c8de944876"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra28905c8de944876"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb394bcf15b64420"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reb394bcf15b64420"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e17cd686a624ebb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e17cd686a624ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4305bfebe8e1484b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4305bfebe8e1484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R29254230a3714e92"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R29254230a3714e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R463e7b4a63504262"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R463e7b4a63504262"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R58808fbcedc64e6d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R58808fbcedc64e6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ca7396d6e99499f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ca7396d6e99499f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec2a512aca9e4f62"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec2a512aca9e4f62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ae81fdec4e34e18"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7ae81fdec4e34e18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R34c9f8e4364a419e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/ConditionalFormat_ColorScale3/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R34c9f8e4364a419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raabbb15e955b4839"/>
   </x:sheets>
 </x:workbook>
 </file>
